--- a/DATA/demand/Base_demand_80_percent_scenario.xlsx
+++ b/DATA/demand/Base_demand_80_percent_scenario.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/demand/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{3770FA51-1088-4802-B5BB-F1618DBE5D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E14955DB-FEAB-4D18-A92C-ACE72DDAFF77}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{3770FA51-1088-4802-B5BB-F1618DBE5D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F53B9E4C-27DE-458B-BDB8-992B2C8E731C}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{7F70F032-7082-4611-84B0-311287B5CE5B}"/>
+    <workbookView xWindow="13550" yWindow="-7070" windowWidth="38620" windowHeight="21100" xr2:uid="{7F70F032-7082-4611-84B0-311287B5CE5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -62,9 +62,6 @@
     <t>Hib</t>
   </si>
   <si>
-    <t>IPV</t>
-  </si>
-  <si>
     <t>HPV</t>
   </si>
   <si>
@@ -72,6 +69,9 @@
   </si>
   <si>
     <t>PCV</t>
+  </si>
+  <si>
+    <t>Polio</t>
   </si>
 </sst>
 </file>
@@ -800,7 +800,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B10" s="6">
         <v>522182008.89205372</v>
@@ -835,7 +835,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="7">
         <v>18988209.721337222</v>
@@ -870,7 +870,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="7">
         <v>142479003.36778629</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="7">
         <v>160800233.02991807</v>
